--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED77C001-27D8-4D9B-B6C8-538EEC83D0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE95BCCD-B9F7-47AA-A144-1253211D1536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -817,7 +817,6 @@
         <v>0</v>
       </c>
       <c r="M2" s="20">
-        <f>K2-L2</f>
         <v>0</v>
       </c>
       <c r="N2" s="7"/>
@@ -862,18 +861,18 @@
         <v>1267546.8</v>
       </c>
       <c r="K3" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L3" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M3" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="20">
         <f>K3-L3-M3</f>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="27" x14ac:dyDescent="0.25">
@@ -912,18 +911,18 @@
         <v>1191268.6266666665</v>
       </c>
       <c r="K4" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L4" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M4" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="20">
         <f t="shared" ref="O4:O22" si="2">K4-L4-M4</f>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="27" x14ac:dyDescent="0.25">
@@ -962,18 +961,18 @@
         <v>984863.8</v>
       </c>
       <c r="K5" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M5" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="20">
         <f t="shared" si="2"/>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -1012,18 +1011,18 @@
         <v>1399651.8</v>
       </c>
       <c r="K6" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L6" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M6" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="20">
         <f t="shared" si="2"/>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1062,18 +1061,18 @@
         <v>1485968.6266666665</v>
       </c>
       <c r="K7" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L7" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M7" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="20">
         <f t="shared" si="2"/>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="27" x14ac:dyDescent="0.25">
@@ -1162,18 +1161,18 @@
         <v>1129915.8666666667</v>
       </c>
       <c r="K9" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L9" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M9" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N9" s="7"/>
       <c r="O9" s="20">
         <f>K9-L9-M9</f>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1212,18 +1211,18 @@
         <v>1124963.8</v>
       </c>
       <c r="K10" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M10" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N10" s="7"/>
       <c r="O10" s="20">
         <f t="shared" si="2"/>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1260,18 +1259,18 @@
         <v>822022.63333333342</v>
       </c>
       <c r="K11" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="6">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="M11" s="20">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="20">
         <f t="shared" si="2"/>
-        <v>493000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1534,7 +1533,7 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E17" s="6">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6">
         <f t="shared" si="0"/>
@@ -1551,7 +1550,7 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="1"/>
-        <v>1229963.8</v>
+        <v>729963.8</v>
       </c>
       <c r="K17" s="6">
         <v>0</v>
@@ -1634,7 +1633,7 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E19" s="6">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6">
         <f t="shared" si="0"/>
@@ -1651,7 +1650,7 @@
       </c>
       <c r="J19" s="6">
         <f t="shared" si="1"/>
-        <v>1109963.8</v>
+        <v>709963.8</v>
       </c>
       <c r="K19" s="6">
         <v>0</v>
@@ -1732,7 +1731,7 @@
         <v>99638</v>
       </c>
       <c r="E21" s="6">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="F21" s="6">
         <f t="shared" si="0"/>
@@ -1749,7 +1748,7 @@
       </c>
       <c r="J21" s="6">
         <f t="shared" si="1"/>
-        <v>973971.04</v>
+        <v>723971.04</v>
       </c>
       <c r="K21" s="6">
         <v>0</v>
@@ -1782,7 +1781,7 @@
         <v>24909.5</v>
       </c>
       <c r="E22" s="6">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="F22" s="6">
         <f t="shared" si="0"/>
@@ -1799,7 +1798,7 @@
       </c>
       <c r="J22" s="6">
         <f t="shared" si="1"/>
-        <v>3665992.76</v>
+        <v>165992.76</v>
       </c>
       <c r="K22" s="6">
         <v>0</v>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\datosn\Documents\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE95BCCD-B9F7-47AA-A144-1253211D1536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A925D4-93C2-4070-A1CD-D61C4E6C1F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>CEDULA</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>DESCUENTOS EF</t>
+  </si>
+  <si>
+    <t>hola</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1022,9 @@
       <c r="M6" s="20">
         <v>0</v>
       </c>
-      <c r="N6" s="7"/>
+      <c r="N6" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="O6" s="20">
         <f t="shared" si="2"/>
         <v>0</v>
